--- a/data/trans_dic/P43C-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42,71%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,37%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,39; 30,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,14; 44,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,43; 47,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,96; 23,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,7; 30,72</t>
+          <t>22,39; 30,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,56; 43,64</t>
+          <t>34,14; 44,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,8; 48,02</t>
+          <t>37,43; 47,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 23,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22,7; 30,72</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34,56; 43,64</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37,8; 48,02</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,14; 23,0</t>
+          <t>10,96; 23,06</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>61,98%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62,87%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74,62%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67,5%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>61,98%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,78; 66,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>70,74; 78,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,89; 71,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,93; 79,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,53; 67,02</t>
+          <t>58,78; 66,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,72; 78,04</t>
+          <t>70,74; 78,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,8; 71,29</t>
+          <t>63,89; 71,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,28; 77,71</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>58,53; 67,02</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>70,72; 78,04</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>63,8; 71,29</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>52,28; 77,71</t>
+          <t>51,93; 79,91</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>69,18%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,18%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,93; 74,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78,01; 84,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>75,87; 81,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,81; 73,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,12; 75,1</t>
+          <t>67,93; 74,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,17; 84,26</t>
+          <t>78,01; 84,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,7; 81,84</t>
+          <t>75,87; 81,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65,53; 72,9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>68,12; 75,1</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>78,17; 84,26</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>75,7; 81,84</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>65,53; 72,9</t>
+          <t>64,81; 73,01</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77,54%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76,6%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>77,54%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,26; 75,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,63; 83,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,08; 80,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,05; 82,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,87; 76,19</t>
+          <t>68,26; 75,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,38; 82,81</t>
+          <t>76,63; 83,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,21; 79,89</t>
+          <t>73,08; 80,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74,41; 82,33</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67,87; 76,19</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76,38; 82,81</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73,21; 79,89</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,41; 82,33</t>
+          <t>74,05; 82,15</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>71,72%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>67,4%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>71,15%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,28; 61,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,88; 76,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,7; 71,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,7; 74,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,52; 60,91</t>
+          <t>51,28; 61,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,11; 76,34</t>
+          <t>66,88; 76,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,8; 71,99</t>
+          <t>62,7; 71,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,84; 74,39</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51,52; 60,91</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>67,11; 76,34</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62,8; 71,99</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>67,84; 74,39</t>
+          <t>67,7; 74,61</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>51,56%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>37,91%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,67; 43,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,7; 56,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,74; 62,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,47; 63,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,9; 43,39</t>
+          <t>33,67; 43,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,27; 57,19</t>
+          <t>45,7; 56,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,89; 63,13</t>
+          <t>52,74; 62,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,59; 63,63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>33,9; 43,39</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>46,27; 57,19</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>52,89; 63,13</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>14,59; 63,63</t>
+          <t>14,47; 63,63</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,01%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,77; 24,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,53; 34,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,95; 41,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,32; 48,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,95; 24,86</t>
+          <t>15,77; 24,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,36; 34,4</t>
+          <t>24,53; 34,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,26; 41,64</t>
+          <t>29,95; 41,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,04; 47,64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>15,95; 24,86</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>24,36; 34,4</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30,26; 41,64</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,04; 47,64</t>
+          <t>40,32; 48,18</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1313,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,26 +1347,6 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>55,97%</t>
         </is>
@@ -1697,62 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,41; 66,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,28; 65,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,03; 61,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,98; 55,46</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,58; 66,93</t>
+          <t>63,41; 66,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,29; 65,57</t>
+          <t>62,28; 65,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,79; 61,47</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>51,98; 55,46</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>63,58; 66,93</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>62,29; 65,57</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>43,79; 61,47</t>
+          <t>42,03; 61,37</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1408,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
@@ -1788,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1801,22 +1444,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1824,20 +1463,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1878,26 +1509,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1914,10 +1525,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1932,22 +1539,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1966,26 +1573,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -2000,22 +1587,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122846</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167377</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2034,26 +1621,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>122846</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>167377</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>164759</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43181</t>
         </is>
@@ -2068,62 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>103425; 141379</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>145887; 188882</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>144373; 183076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28925; 60849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>104830; 141864</t>
+          <t>103425; 141379</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147686; 186463</t>
+          <t>145887; 188882</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>145799; 185224</t>
+          <t>144373; 183076</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29403; 60689</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104830; 141864</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147686; 186463</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145799; 185224</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>29403; 60689</t>
+          <t>28925; 60849</t>
         </is>
       </c>
     </row>
@@ -2140,22 +1687,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>422</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2174,26 +1721,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>171</t>
         </is>
@@ -2208,22 +1735,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>389496</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452021</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2242,26 +1769,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>244923</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>389496</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>452021</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>379048</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>244923</t>
         </is>
@@ -2276,62 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>364158; 411374</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>428527; 473668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>358801; 401199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>205197; 315760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>362578; 415199</t>
+          <t>364158; 411374</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>428393; 472779</t>
+          <t>428527; 473668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>358293; 400353</t>
+          <t>358801; 401199</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>206597; 307063</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>362578; 415199</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>428393; 472779</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>358293; 400353</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>206597; 307063</t>
+          <t>205197; 315760</t>
         </is>
       </c>
     </row>
@@ -2348,22 +1835,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>540</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2382,26 +1869,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>394</t>
         </is>
@@ -2416,22 +1883,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492505</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>575284</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>518258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2450,26 +1917,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255882</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>492505</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>575284</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>518258</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>255882</t>
         </is>
@@ -2484,62 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>466663; 514168</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>550619; 595476</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>498529; 538421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>239703; 270023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>467949; 515877</t>
+          <t>466663; 514168</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>551757; 594715</t>
+          <t>550619; 595476</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>497429; 537733</t>
+          <t>498529; 538421</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>242388; 269625</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>467949; 515877</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>551757; 594715</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>497429; 537733</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>242388; 269625</t>
+          <t>239703; 270023</t>
         </is>
       </c>
     </row>
@@ -2556,22 +1983,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>427</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2590,26 +2017,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>587</t>
         </is>
@@ -2624,22 +2031,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366661</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492093</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2658,26 +2065,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>388218</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>366661</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>492093</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>492828</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>388218</t>
         </is>
@@ -2692,62 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>346205; 385276</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>472169; 513169</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>470218; 515858</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>370778; 411291</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>344226; 386429</t>
+          <t>346205; 385276</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>470647; 510304</t>
+          <t>472169; 513169</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>471011; 514039</t>
+          <t>470218; 515858</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>372565; 412192</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>344226; 386429</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>470647; 510304</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>471011; 514039</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>372565; 412192</t>
+          <t>370778; 411291</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2131,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2798,26 +2165,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>516</t>
         </is>
@@ -2832,22 +2179,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223832</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316156</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2866,26 +2213,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>284328</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>223832</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>316156</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>332757</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>284328</t>
         </is>
@@ -2900,62 +2227,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>203004; 242805</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>294813; 335677</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>309541; 353281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>270551; 298159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>203931; 241112</t>
+          <t>203004; 242805</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>295808; 336505</t>
+          <t>294813; 335677</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>310072; 355432</t>
+          <t>309541; 353281</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>271118; 297299</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>203931; 241112</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>295808; 336505</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>310072; 355432</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>271118; 297299</t>
+          <t>270551; 298159</t>
         </is>
       </c>
     </row>
@@ -2972,22 +2279,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>405</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3006,26 +2313,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>405</t>
         </is>
@@ -3040,22 +2327,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130436</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179974</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3074,26 +2361,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>197491</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>130436</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>179974</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>216106</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>197491</t>
         </is>
@@ -3108,62 +2375,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>113021; 147547</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>159511; 198804</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>196563; 234216</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>75403; 331477</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>113786; 145635</t>
+          <t>113021; 147547</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>161520; 199639</t>
+          <t>159511; 198804</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>197102; 235284</t>
+          <t>196563; 234216</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>76015; 331484</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>113786; 145635</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>161520; 199639</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>197102; 235284</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>76015; 331484</t>
+          <t>75403; 331477</t>
         </is>
       </c>
     </row>
@@ -3180,22 +2427,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3214,26 +2461,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>319</t>
         </is>
@@ -3248,22 +2475,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110072</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3282,26 +2509,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>157265</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>64572</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>110072</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>138471</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>157265</t>
         </is>
@@ -3316,62 +2523,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50473; 79450</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92559; 129598</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>117551; 162205</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>144059; 172165</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51057; 79567</t>
+          <t>50473; 79450</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91925; 129791</t>
+          <t>92559; 129598</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>118747; 163426</t>
+          <t>117551; 162205</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>143071; 170220</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>51057; 79567</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>91925; 129791</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>118747; 163426</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>143071; 170220</t>
+          <t>144059; 172165</t>
         </is>
       </c>
     </row>
@@ -3388,22 +2575,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3422,26 +2609,6 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2420</t>
         </is>
@@ -3456,22 +2623,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790349</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2292976</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2242226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571289</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3490,26 +2657,6 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1571289</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1790349</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2292976</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2242226</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>1571289</t>
         </is>
@@ -3524,62 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2233561; 2345963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2183875; 2297736</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1180025; 1722853</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1729293; 1845045</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2239652; 2357380</t>
+          <t>2233561; 2345963</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2184223; 2299181</t>
+          <t>2183875; 2297736</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1229447; 1725596</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1729293; 1845045</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2239652; 2357380</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2184223; 2299181</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>1229447; 1725596</t>
+          <t>1180025; 1722853</t>
         </is>
       </c>
     </row>
@@ -3591,17 +2718,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P43C-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Edad-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,39; 30,61</t>
+          <t>22,99; 30,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,14; 44,2</t>
+          <t>34,31; 44,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,43; 47,46</t>
+          <t>37,84; 47,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 23,06</t>
+          <t>11,08; 22,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,39; 30,61</t>
+          <t>22,99; 30,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,14; 44,2</t>
+          <t>34,31; 44,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,43; 47,46</t>
+          <t>37,84; 47,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 23,06</t>
+          <t>11,08; 22,38</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,78; 66,4</t>
+          <t>58,84; 66,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,74; 78,19</t>
+          <t>70,76; 78,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,89; 71,44</t>
+          <t>63,06; 71,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,93; 79,91</t>
+          <t>46,2; 57,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,78; 66,4</t>
+          <t>58,84; 66,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,74; 78,19</t>
+          <t>70,76; 78,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,89; 71,44</t>
+          <t>63,06; 71,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,93; 79,91</t>
+          <t>46,2; 57,87</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,93; 74,85</t>
+          <t>68,01; 75,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,01; 84,36</t>
+          <t>78,36; 84,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,87; 81,94</t>
+          <t>75,55; 81,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64,81; 73,01</t>
+          <t>64,26; 72,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,93; 74,85</t>
+          <t>68,01; 75,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,01; 84,36</t>
+          <t>78,36; 84,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,87; 81,94</t>
+          <t>75,55; 81,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,81; 73,01</t>
+          <t>64,26; 72,16</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,26; 75,96</t>
+          <t>67,9; 75,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,63; 83,28</t>
+          <t>76,1; 83,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,08; 80,18</t>
+          <t>73,0; 79,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,05; 82,15</t>
+          <t>72,24; 78,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,26; 75,96</t>
+          <t>67,9; 75,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,63; 83,28</t>
+          <t>76,1; 83,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,08; 80,18</t>
+          <t>73,0; 79,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74,05; 82,15</t>
+          <t>72,24; 78,13</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,28; 61,34</t>
+          <t>51,68; 61,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,88; 76,15</t>
+          <t>67,25; 75,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,7; 71,56</t>
+          <t>63,03; 71,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,7; 74,61</t>
+          <t>67,31; 74,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,28; 61,34</t>
+          <t>51,68; 61,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,88; 76,15</t>
+          <t>67,25; 75,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,7; 71,56</t>
+          <t>63,03; 71,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,7; 74,61</t>
+          <t>67,31; 74,21</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,67; 43,96</t>
+          <t>34,43; 44,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,7; 56,95</t>
+          <t>46,47; 56,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,74; 62,84</t>
+          <t>52,88; 63,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,47; 63,63</t>
+          <t>58,67; 66,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,67; 43,96</t>
+          <t>34,43; 44,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,7; 56,95</t>
+          <t>46,47; 56,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,74; 62,84</t>
+          <t>52,88; 63,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,47; 63,63</t>
+          <t>58,67; 66,26</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 24,83</t>
+          <t>15,79; 25,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,53; 34,35</t>
+          <t>24,37; 34,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,95; 41,33</t>
+          <t>30,33; 41,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,32; 48,18</t>
+          <t>39,8; 47,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 24,83</t>
+          <t>15,79; 25,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,53; 34,35</t>
+          <t>24,37; 34,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,95; 41,33</t>
+          <t>30,33; 41,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,32; 48,18</t>
+          <t>39,8; 47,39</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,41; 66,6</t>
+          <t>63,41; 66,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,52</t>
+          <t>62,12; 65,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42,03; 61,37</t>
+          <t>56,26; 59,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,41; 66,6</t>
+          <t>63,41; 66,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,52</t>
+          <t>62,12; 65,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,03; 61,37</t>
+          <t>56,26; 59,78</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
     </row>
@@ -1635,42 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>103425; 141379</t>
+          <t>106186; 141056</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145887; 188882</t>
+          <t>146594; 188693</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>144373; 183076</t>
+          <t>145943; 183449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28925; 60849</t>
+          <t>33483; 67664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>103425; 141379</t>
+          <t>106186; 141056</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>145887; 188882</t>
+          <t>146594; 188693</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>144373; 183076</t>
+          <t>145943; 183449</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28925; 60849</t>
+          <t>33483; 67664</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
     </row>
@@ -1783,42 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>364158; 411374</t>
+          <t>364502; 413265</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>428527; 473668</t>
+          <t>428657; 473773</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>358801; 401199</t>
+          <t>354155; 399673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205197; 315760</t>
+          <t>170079; 213019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>364158; 411374</t>
+          <t>364502; 413265</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>428527; 473668</t>
+          <t>428657; 473773</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>358801; 401199</t>
+          <t>354155; 399673</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>205197; 315760</t>
+          <t>170079; 213019</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
     </row>
@@ -1931,42 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>466663; 514168</t>
+          <t>467211; 516725</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>550619; 595476</t>
+          <t>553129; 596372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498529; 538421</t>
+          <t>496393; 536258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239703; 270023</t>
+          <t>272034; 305486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>466663; 514168</t>
+          <t>467211; 516725</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>550619; 595476</t>
+          <t>553129; 596372</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>498529; 538421</t>
+          <t>496393; 536258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>239703; 270023</t>
+          <t>272034; 305486</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>388218</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>388218</t>
+          <t>380803</t>
         </is>
       </c>
     </row>
@@ -2079,42 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>346205; 385276</t>
+          <t>344386; 385357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>472169; 513169</t>
+          <t>468957; 512849</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>470218; 515858</t>
+          <t>469659; 512643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>370778; 411291</t>
+          <t>366314; 396163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>346205; 385276</t>
+          <t>344386; 385357</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>472169; 513169</t>
+          <t>468957; 512849</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>470218; 515858</t>
+          <t>469659; 512643</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>370778; 411291</t>
+          <t>366314; 396163</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284328</t>
+          <t>314100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>284328</t>
+          <t>314100</t>
         </is>
       </c>
     </row>
@@ -2227,42 +2227,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>203004; 242805</t>
+          <t>204580; 243534</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>294813; 335677</t>
+          <t>296434; 333458</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>309541; 353281</t>
+          <t>311211; 355169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>270551; 298159</t>
+          <t>299334; 330013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>203004; 242805</t>
+          <t>204580; 243534</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>294813; 335677</t>
+          <t>296434; 333458</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>309541; 353281</t>
+          <t>311211; 355169</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>270551; 298159</t>
+          <t>299334; 330013</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
     </row>
@@ -2375,42 +2375,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>113021; 147547</t>
+          <t>115570; 149587</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>159511; 198804</t>
+          <t>162209; 198343</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196563; 234216</t>
+          <t>197089; 234981</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75403; 331477</t>
+          <t>202590; 228787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>113021; 147547</t>
+          <t>115570; 149587</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>159511; 198804</t>
+          <t>162209; 198343</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>196563; 234216</t>
+          <t>197089; 234981</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>75403; 331477</t>
+          <t>202590; 228787</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>170713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>170713</t>
         </is>
       </c>
     </row>
@@ -2523,42 +2523,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50473; 79450</t>
+          <t>50540; 80696</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92559; 129598</t>
+          <t>91953; 129061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117551; 162205</t>
+          <t>119021; 163291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144059; 172165</t>
+          <t>154859; 184391</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>50473; 79450</t>
+          <t>50540; 80696</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92559; 129598</t>
+          <t>91953; 129061</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>117551; 162205</t>
+          <t>119021; 163291</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>144059; 172165</t>
+          <t>154859; 184391</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
     </row>
@@ -2671,42 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2233561; 2345963</t>
+          <t>2233642; 2354668</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2183875; 2297736</t>
+          <t>2178249; 2294711</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1180025; 1722853</t>
+          <t>1564073; 1661715</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2233561; 2345963</t>
+          <t>2233642; 2354668</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2183875; 2297736</t>
+          <t>2178249; 2294711</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1180025; 1722853</t>
+          <t>1564073; 1661715</t>
         </is>
       </c>
     </row>
